--- a/БД/funcs/T_LVALH.xlsx
+++ b/БД/funcs/T_LVALH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28290" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="4" r:id="rId1"/>
@@ -866,7 +866,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -900,6 +900,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -965,7 +971,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1129,14 +1135,17 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1541,15 +1550,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
+      <c r="AZ1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="61"/>
+      <c r="BB1" s="61"/>
+      <c r="BC1" s="61"/>
+      <c r="BD1" s="61"/>
+      <c r="BE1" s="61"/>
+      <c r="BF1" s="61"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -18140,22 +18149,20 @@
       <c r="AS3" s="31">
         <v>0</v>
       </c>
-      <c r="AT3" s="31">
-        <v>0</v>
+      <c r="AT3" s="62">
+        <v>1</v>
       </c>
       <c r="AU3" s="31">
         <v>0</v>
       </c>
-      <c r="AV3" s="31">
-        <f t="shared" ref="AV3" si="2">BIN2DEC(CONCATENATE(0,0,0,0,AR3,AS3,AT3,AU3))</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="31">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="31">
-        <f t="shared" ref="AX3:AX40" si="3">BIN2DEC(CONCATENATE(0,0,0,0,AT3,AU3,AV3,AW3))</f>
-        <v>0</v>
+      <c r="AV3" s="62">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="62">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="62">
+        <v>1</v>
       </c>
       <c r="AY3" s="31"/>
       <c r="AZ3" s="28"/>
@@ -18166,7 +18173,7 @@
       <c r="BE3" s="35"/>
       <c r="BF3" s="31"/>
       <c r="BG3" s="36" t="str">
-        <f t="shared" ref="BG3" si="4">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
+        <f t="shared" ref="BG3" si="2">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
         <v>description: "Вывод терминала", note: "Вывод терминала", group: "control", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH3" s="37"/>
@@ -18189,7 +18196,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="25">
-        <f t="shared" ref="I4:I6" si="5">LEN(F4)</f>
+        <f t="shared" ref="I4:I6" si="3">LEN(F4)</f>
         <v>12</v>
       </c>
       <c r="J4" s="25" t="str">
@@ -18270,14 +18277,14 @@
         <v>0</v>
       </c>
       <c r="AV4" s="31">
-        <f t="shared" ref="AV4:AV6" si="6">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
+        <f t="shared" ref="AV4:AV6" si="4">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
         <v>0</v>
       </c>
       <c r="AW4" s="31">
         <v>0</v>
       </c>
       <c r="AX4" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AX3:AX40" si="5">BIN2DEC(CONCATENATE(0,0,0,0,AT4,AU4,AV4,AW4))</f>
         <v>0</v>
       </c>
       <c r="AY4" s="31"/>
@@ -18289,7 +18296,7 @@
       <c r="BE4" s="35"/>
       <c r="BF4" s="31"/>
       <c r="BG4" s="36" t="str">
-        <f t="shared" ref="BG4:BG6" si="7">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
+        <f t="shared" ref="BG4:BG6" si="6">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
         <v>description: "Сраб.сигн ТО", note: "Срабатывание ТО на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH4" s="37"/>
@@ -18312,7 +18319,7 @@
       </c>
       <c r="H5" s="25"/>
       <c r="I5" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="J5" s="25" t="str">
@@ -18393,14 +18400,14 @@
         <v>0</v>
       </c>
       <c r="AV5" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW5" s="31">
         <v>0</v>
       </c>
       <c r="AX5" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY5" s="31"/>
@@ -18412,7 +18419,7 @@
       <c r="BE5" s="35"/>
       <c r="BF5" s="31"/>
       <c r="BG5" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Сраб.сигн МТЗ 1ст.", note: "Срабатывание 1 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH5" s="37"/>
@@ -18435,7 +18442,7 @@
       </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="J6" s="25" t="str">
@@ -18516,14 +18523,14 @@
         <v>0</v>
       </c>
       <c r="AV6" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AW6" s="31">
         <v>0</v>
       </c>
       <c r="AX6" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY6" s="31"/>
@@ -18535,7 +18542,7 @@
       <c r="BE6" s="35"/>
       <c r="BF6" s="31"/>
       <c r="BG6" s="36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>description: "Сраб.сигн МТЗ 2ст.", note: "Срабатывание 2 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH6" s="37"/>
@@ -18558,7 +18565,7 @@
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <f t="shared" ref="I7:I8" si="8">LEN(F7)</f>
+        <f t="shared" ref="I7:I8" si="7">LEN(F7)</f>
         <v>18</v>
       </c>
       <c r="J7" s="25" t="str">
@@ -18639,14 +18646,14 @@
         <v>0</v>
       </c>
       <c r="AV7" s="31">
-        <f t="shared" ref="AV7:AV8" si="9">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
+        <f t="shared" ref="AV7:AV8" si="8">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
         <v>0</v>
       </c>
       <c r="AW7" s="31">
         <v>0</v>
       </c>
       <c r="AX7" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY7" s="31"/>
@@ -18658,7 +18665,7 @@
       <c r="BE7" s="35"/>
       <c r="BF7" s="31"/>
       <c r="BG7" s="36" t="str">
-        <f t="shared" ref="BG7:BG8" si="10">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
+        <f t="shared" ref="BG7:BG8" si="9">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
         <v>description: "Сраб.сигн МТЗ 3ст.", note: "Срабатывание 3 ступени МТЗ на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH7" s="37"/>
@@ -18681,7 +18688,7 @@
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="J8" s="25" t="str">
@@ -18762,14 +18769,14 @@
         <v>0</v>
       </c>
       <c r="AV8" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AW8" s="31">
         <v>0</v>
       </c>
       <c r="AX8" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY8" s="31"/>
@@ -18781,7 +18788,7 @@
       <c r="BE8" s="35"/>
       <c r="BF8" s="31"/>
       <c r="BG8" s="36" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>description: "Сраб.сигн ЛО ГЗсигн", note: "Срабатывание ЛО ГЗсигн на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH8" s="37"/>
@@ -18804,11 +18811,11 @@
       </c>
       <c r="H9" s="25"/>
       <c r="I9" s="25">
-        <f t="shared" ref="I9:I33" si="11">LEN(F9)</f>
+        <f t="shared" ref="I9:I33" si="10">LEN(F9)</f>
         <v>19</v>
       </c>
       <c r="J9" s="25" t="str">
-        <f t="shared" ref="J9:J33" si="12">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
+        <f t="shared" ref="J9:J33" si="11">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
         <v>Сраб.сигн ЛО ГЗоткл</v>
       </c>
       <c r="K9" s="23" t="s">
@@ -18885,14 +18892,14 @@
         <v>0</v>
       </c>
       <c r="AV9" s="31">
-        <f t="shared" ref="AV9:AV33" si="13">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
+        <f t="shared" ref="AV9:AV33" si="12">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
         <v>0</v>
       </c>
       <c r="AW9" s="31">
         <v>0</v>
       </c>
       <c r="AX9" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY9" s="31"/>
@@ -18904,7 +18911,7 @@
       <c r="BE9" s="35"/>
       <c r="BF9" s="31"/>
       <c r="BG9" s="36" t="str">
-        <f t="shared" ref="BG9:BG33" si="14">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
+        <f t="shared" ref="BG9:BG33" si="13">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
         <v>description: "Сраб.сигн ЛО ГЗоткл", note: "Срабатывание ЛО ГЗоткл на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH9" s="37"/>
@@ -18927,11 +18934,11 @@
       </c>
       <c r="H10" s="25"/>
       <c r="I10" s="25">
+        <f t="shared" si="10"/>
+        <v>19</v>
+      </c>
+      <c r="J10" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>19</v>
-      </c>
-      <c r="J10" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ГЗ РПН</v>
       </c>
       <c r="K10" s="23" t="s">
@@ -19008,14 +19015,14 @@
         <v>0</v>
       </c>
       <c r="AV10" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW10" s="31">
         <v>0</v>
       </c>
       <c r="AX10" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY10" s="31"/>
@@ -19027,7 +19034,7 @@
       <c r="BE10" s="35"/>
       <c r="BF10" s="31"/>
       <c r="BG10" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ГЗ РПН", note: "Срабатывание ЛО ГЗ РПН на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH10" s="37"/>
@@ -19050,11 +19057,11 @@
       </c>
       <c r="H11" s="25"/>
       <c r="I11" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J11" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J11" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДТм</v>
       </c>
       <c r="K11" s="23" t="s">
@@ -19131,14 +19138,14 @@
         <v>0</v>
       </c>
       <c r="AV11" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW11" s="31">
         <v>0</v>
       </c>
       <c r="AX11" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY11" s="31"/>
@@ -19150,7 +19157,7 @@
       <c r="BE11" s="35"/>
       <c r="BF11" s="31"/>
       <c r="BG11" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДТм", note: "Срабатывание ЛО ДТм", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH11" s="37"/>
@@ -19173,11 +19180,11 @@
       </c>
       <c r="H12" s="25"/>
       <c r="I12" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J12" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДТо</v>
       </c>
       <c r="K12" s="23" t="s">
@@ -19254,14 +19261,14 @@
         <v>0</v>
       </c>
       <c r="AV12" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW12" s="31">
         <v>0</v>
       </c>
       <c r="AX12" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY12" s="31"/>
@@ -19273,7 +19280,7 @@
       <c r="BE12" s="35"/>
       <c r="BF12" s="31"/>
       <c r="BG12" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДТо", note: "Срабатывание ЛО ДТо", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH12" s="37"/>
@@ -19296,11 +19303,11 @@
       </c>
       <c r="H13" s="25"/>
       <c r="I13" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J13" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J13" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО РД</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -19377,14 +19384,14 @@
         <v>0</v>
       </c>
       <c r="AV13" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW13" s="31">
         <v>0</v>
       </c>
       <c r="AX13" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY13" s="31"/>
@@ -19396,7 +19403,7 @@
       <c r="BE13" s="35"/>
       <c r="BF13" s="31"/>
       <c r="BG13" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО РД", note: "Срабатывание ЛО РД на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH13" s="37"/>
@@ -19419,11 +19426,11 @@
       </c>
       <c r="H14" s="25"/>
       <c r="I14" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J14" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J14" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ПК</v>
       </c>
       <c r="K14" s="23" t="s">
@@ -19500,14 +19507,14 @@
         <v>0</v>
       </c>
       <c r="AV14" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW14" s="31">
         <v>0</v>
       </c>
       <c r="AX14" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY14" s="31"/>
@@ -19519,7 +19526,7 @@
       <c r="BE14" s="35"/>
       <c r="BF14" s="31"/>
       <c r="BG14" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ПК", note: "Срабатывание ЛО ПК на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH14" s="37"/>
@@ -19542,11 +19549,11 @@
       </c>
       <c r="H15" s="25"/>
       <c r="I15" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J15" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J15" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ОК</v>
       </c>
       <c r="K15" s="23" t="s">
@@ -19623,14 +19630,14 @@
         <v>0</v>
       </c>
       <c r="AV15" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW15" s="31">
         <v>0</v>
       </c>
       <c r="AX15" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY15" s="31"/>
@@ -19642,7 +19649,7 @@
       <c r="BE15" s="35"/>
       <c r="BF15" s="31"/>
       <c r="BG15" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ОК", note: "Срабатывание ЛО ОК на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH15" s="37"/>
@@ -19665,11 +19672,11 @@
       </c>
       <c r="H16" s="25"/>
       <c r="I16" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J16" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J16" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЛО ДУм Р</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -19746,14 +19753,14 @@
         <v>0</v>
       </c>
       <c r="AV16" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW16" s="31">
         <v>0</v>
       </c>
       <c r="AX16" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY16" s="31"/>
@@ -19765,7 +19772,7 @@
       <c r="BE16" s="35"/>
       <c r="BF16" s="31"/>
       <c r="BG16" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЛО ДУм Р", note: "Срабатывание ЛО ДУм расширителя на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH16" s="37"/>
@@ -19788,11 +19795,11 @@
       </c>
       <c r="H17" s="25"/>
       <c r="I17" s="25">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="J17" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="J17" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЗП</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -19869,14 +19876,14 @@
         <v>0</v>
       </c>
       <c r="AV17" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW17" s="31">
         <v>0</v>
       </c>
       <c r="AX17" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY17" s="31"/>
@@ -19888,7 +19895,7 @@
       <c r="BE17" s="35"/>
       <c r="BF17" s="31"/>
       <c r="BG17" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЗП", note: "Срабатывание ЗП", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH17" s="37"/>
@@ -19911,11 +19918,11 @@
       </c>
       <c r="H18" s="25"/>
       <c r="I18" s="25">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="J18" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>13</v>
-      </c>
-      <c r="J18" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб.сигн ЗОП</v>
       </c>
       <c r="K18" s="23" t="s">
@@ -19992,14 +19999,14 @@
         <v>0</v>
       </c>
       <c r="AV18" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW18" s="31">
         <v>0</v>
       </c>
       <c r="AX18" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY18" s="31"/>
@@ -20011,7 +20018,7 @@
       <c r="BE18" s="35"/>
       <c r="BF18" s="31"/>
       <c r="BG18" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб.сигн ЗОП", note: "Срабатывание ЗОП на сигнал", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH18" s="37"/>
@@ -20034,11 +20041,11 @@
       </c>
       <c r="H19" s="25"/>
       <c r="I19" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J19" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J19" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Неисправность ЦН</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -20115,14 +20122,14 @@
         <v>0</v>
       </c>
       <c r="AV19" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW19" s="31">
         <v>0</v>
       </c>
       <c r="AX19" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY19" s="31"/>
@@ -20134,7 +20141,7 @@
       <c r="BE19" s="35"/>
       <c r="BF19" s="31"/>
       <c r="BG19" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Неисправность ЦН", note: "Неисправность цепей напряжения", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH19" s="37"/>
@@ -20157,11 +20164,11 @@
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="25">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J20" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="J20" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. ЛО Т</v>
       </c>
       <c r="K20" s="23" t="s">
@@ -20238,14 +20245,14 @@
         <v>0</v>
       </c>
       <c r="AV20" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW20" s="31">
         <v>0</v>
       </c>
       <c r="AX20" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY20" s="31"/>
@@ -20257,7 +20264,7 @@
       <c r="BE20" s="35"/>
       <c r="BF20" s="31"/>
       <c r="BG20" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. ЛО Т", note: "Срабатывание общей логики отключения трансформатора", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH20" s="37"/>
@@ -20280,11 +20287,11 @@
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="25">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="J21" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="J21" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. УРОВ</v>
       </c>
       <c r="K21" s="23" t="s">
@@ -20361,14 +20368,14 @@
         <v>0</v>
       </c>
       <c r="AV21" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW21" s="31">
         <v>0</v>
       </c>
       <c r="AX21" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY21" s="31"/>
@@ -20380,7 +20387,7 @@
       <c r="BE21" s="35"/>
       <c r="BF21" s="31"/>
       <c r="BG21" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. УРОВ", note: "Срабатывание УРОВ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH21" s="37"/>
@@ -20403,11 +20410,11 @@
       </c>
       <c r="H22" s="25"/>
       <c r="I22" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J22" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J22" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Сраб. УРОВ на себя</v>
       </c>
       <c r="K22" s="23" t="s">
@@ -20484,14 +20491,14 @@
         <v>0</v>
       </c>
       <c r="AV22" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW22" s="31">
         <v>0</v>
       </c>
       <c r="AX22" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY22" s="31"/>
@@ -20503,7 +20510,7 @@
       <c r="BE22" s="35"/>
       <c r="BF22" s="31"/>
       <c r="BG22" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Сраб. УРОВ на себя", note: "Срабатывание УРОВ &lt;&lt;на себя&gt;&gt;", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH22" s="37"/>
@@ -20526,11 +20533,11 @@
       </c>
       <c r="H23" s="25"/>
       <c r="I23" s="25">
+        <f t="shared" si="10"/>
+        <v>17</v>
+      </c>
+      <c r="J23" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>17</v>
-      </c>
-      <c r="J23" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Превышен ресурс В</v>
       </c>
       <c r="K23" s="23" t="s">
@@ -20607,14 +20614,14 @@
         <v>0</v>
       </c>
       <c r="AV23" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW23" s="31">
         <v>0</v>
       </c>
       <c r="AX23" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY23" s="31"/>
@@ -20626,7 +20633,7 @@
       <c r="BE23" s="35"/>
       <c r="BF23" s="31"/>
       <c r="BG23" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Превышен ресурс В", note: "Превышен ресурс выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH23" s="37"/>
@@ -20649,11 +20656,11 @@
       </c>
       <c r="H24" s="25"/>
       <c r="I24" s="25">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="J24" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="J24" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Неисправность В</v>
       </c>
       <c r="K24" s="23" t="s">
@@ -20730,14 +20737,14 @@
         <v>0</v>
       </c>
       <c r="AV24" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW24" s="31">
         <v>0</v>
       </c>
       <c r="AX24" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY24" s="31"/>
@@ -20749,7 +20756,7 @@
       <c r="BE24" s="35"/>
       <c r="BF24" s="31"/>
       <c r="BG24" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Неисправность В", note: "Неисправность выключателя", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH24" s="37"/>
@@ -20772,11 +20779,11 @@
       </c>
       <c r="H25" s="25"/>
       <c r="I25" s="25">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="J25" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>18</v>
-      </c>
-      <c r="J25" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>В самопр. отключен</v>
       </c>
       <c r="K25" s="23" t="s">
@@ -20853,14 +20860,14 @@
         <v>0</v>
       </c>
       <c r="AV25" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW25" s="31">
         <v>0</v>
       </c>
       <c r="AX25" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY25" s="31"/>
@@ -20872,7 +20879,7 @@
       <c r="BE25" s="35"/>
       <c r="BF25" s="31"/>
       <c r="BG25" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "В самопр. отключен", note: "Выключатель самопроизвольно отключен", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH25" s="37"/>
@@ -20895,11 +20902,11 @@
       </c>
       <c r="H26" s="25"/>
       <c r="I26" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J26" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J26" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ГЗ сигн</v>
       </c>
       <c r="K26" s="23" t="s">
@@ -20976,14 +20983,14 @@
         <v>0</v>
       </c>
       <c r="AV26" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW26" s="31">
         <v>0</v>
       </c>
       <c r="AX26" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY26" s="31"/>
@@ -20995,7 +21002,7 @@
       <c r="BE26" s="35"/>
       <c r="BF26" s="31"/>
       <c r="BG26" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ГЗ сигн", note: "Сигнализация от ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH26" s="37"/>
@@ -21018,11 +21025,11 @@
       </c>
       <c r="H27" s="25"/>
       <c r="I27" s="25">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="J27" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="J27" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Низ.изол. ГЗ</v>
       </c>
       <c r="K27" s="23" t="s">
@@ -21099,14 +21106,14 @@
         <v>0</v>
       </c>
       <c r="AV27" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW27" s="31">
         <v>0</v>
       </c>
       <c r="AX27" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY27" s="31"/>
@@ -21118,7 +21125,7 @@
       <c r="BE27" s="35"/>
       <c r="BF27" s="31"/>
       <c r="BG27" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Низ.изол. ГЗ", note: "Низкая изоляция ГЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH27" s="37"/>
@@ -21141,11 +21148,11 @@
       </c>
       <c r="H28" s="25"/>
       <c r="I28" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J28" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J28" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ГЗ заблокирована</v>
       </c>
       <c r="K28" s="23" t="s">
@@ -21222,14 +21229,14 @@
         <v>0</v>
       </c>
       <c r="AV28" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW28" s="31">
         <v>0</v>
       </c>
       <c r="AX28" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY28" s="31"/>
@@ -21241,7 +21248,7 @@
       <c r="BE28" s="35"/>
       <c r="BF28" s="31"/>
       <c r="BG28" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ГЗ заблокирована", note: "ГЗ заблокирована", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH28" s="37"/>
@@ -21264,11 +21271,11 @@
       </c>
       <c r="H29" s="25"/>
       <c r="I29" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J29" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J29" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТЗ сигн</v>
       </c>
       <c r="K29" s="23" t="s">
@@ -21345,14 +21352,14 @@
         <v>0</v>
       </c>
       <c r="AV29" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW29" s="31">
         <v>0</v>
       </c>
       <c r="AX29" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY29" s="31"/>
@@ -21364,7 +21371,7 @@
       <c r="BE29" s="35"/>
       <c r="BF29" s="31"/>
       <c r="BG29" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТЗ сигн", note: "Сигнализация от ТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH29" s="37"/>
@@ -21387,11 +21394,11 @@
       </c>
       <c r="H30" s="25"/>
       <c r="I30" s="25">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="J30" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>12</v>
-      </c>
-      <c r="J30" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>Низ.изол. ТЗ</v>
       </c>
       <c r="K30" s="23" t="s">
@@ -21468,14 +21475,14 @@
         <v>0</v>
       </c>
       <c r="AV30" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW30" s="31">
         <v>0</v>
       </c>
       <c r="AX30" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY30" s="31"/>
@@ -21487,7 +21494,7 @@
       <c r="BE30" s="35"/>
       <c r="BF30" s="31"/>
       <c r="BG30" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "Низ.изол. ТЗ", note: "Низкая изоляция ТЗ", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH30" s="37"/>
@@ -21510,11 +21517,11 @@
       </c>
       <c r="H31" s="25"/>
       <c r="I31" s="25">
+        <f t="shared" si="10"/>
+        <v>16</v>
+      </c>
+      <c r="J31" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>16</v>
-      </c>
-      <c r="J31" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТЗ заблокирована</v>
       </c>
       <c r="K31" s="23" t="s">
@@ -21591,14 +21598,14 @@
         <v>0</v>
       </c>
       <c r="AV31" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW31" s="31">
         <v>0</v>
       </c>
       <c r="AX31" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY31" s="31"/>
@@ -21610,7 +21617,7 @@
       <c r="BE31" s="35"/>
       <c r="BF31" s="31"/>
       <c r="BG31" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТЗ заблокирована", note: "ТЗ заблокирована", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH31" s="37"/>
@@ -21633,11 +21640,11 @@
       </c>
       <c r="H32" s="25"/>
       <c r="I32" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J32" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J32" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ТС сигн</v>
       </c>
       <c r="K32" s="23" t="s">
@@ -21714,14 +21721,14 @@
         <v>0</v>
       </c>
       <c r="AV32" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW32" s="31">
         <v>0</v>
       </c>
       <c r="AX32" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY32" s="31"/>
@@ -21733,7 +21740,7 @@
       <c r="BE32" s="35"/>
       <c r="BF32" s="31"/>
       <c r="BG32" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ТС сигн", note: "Сигнализация от ТС", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH32" s="37"/>
@@ -21756,11 +21763,11 @@
       </c>
       <c r="H33" s="25"/>
       <c r="I33" s="25">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="J33" s="25" t="str">
         <f t="shared" si="11"/>
-        <v>7</v>
-      </c>
-      <c r="J33" s="25" t="str">
-        <f t="shared" si="12"/>
         <v>ОТ сигн</v>
       </c>
       <c r="K33" s="23" t="s">
@@ -21837,14 +21844,14 @@
         <v>0</v>
       </c>
       <c r="AV33" s="31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AW33" s="31">
         <v>0</v>
       </c>
       <c r="AX33" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY33" s="31"/>
@@ -21856,7 +21863,7 @@
       <c r="BE33" s="35"/>
       <c r="BF33" s="31"/>
       <c r="BG33" s="36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>description: "ОТ сигн", note: "Контроль оперативного тока", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH33" s="37"/>
@@ -21879,11 +21886,11 @@
       </c>
       <c r="H34" s="25"/>
       <c r="I34" s="25">
-        <f t="shared" ref="I34:I40" si="15">LEN(F34)</f>
+        <f t="shared" ref="I34:I40" si="14">LEN(F34)</f>
         <v>10</v>
       </c>
       <c r="J34" s="25" t="str">
-        <f t="shared" ref="J34:J40" si="16">IF(LEN(F34)&lt;=$J$1,F34,"")</f>
+        <f t="shared" ref="J34:J40" si="15">IF(LEN(F34)&lt;=$J$1,F34,"")</f>
         <v>ОТ НН сигн</v>
       </c>
       <c r="K34" s="23" t="s">
@@ -21960,14 +21967,14 @@
         <v>0</v>
       </c>
       <c r="AV34" s="31">
-        <f t="shared" ref="AV34:AV40" si="17">BIN2DEC(CONCATENATE(0,0,0,0,AR34,AS34,AT34,AU34))</f>
+        <f t="shared" ref="AV34:AV40" si="16">BIN2DEC(CONCATENATE(0,0,0,0,AR34,AS34,AT34,AU34))</f>
         <v>0</v>
       </c>
       <c r="AW34" s="31">
         <v>0</v>
       </c>
       <c r="AX34" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY34" s="31"/>
@@ -21979,7 +21986,7 @@
       <c r="BE34" s="35"/>
       <c r="BF34" s="31"/>
       <c r="BG34" s="36" t="str">
-        <f t="shared" ref="BG34:BG40" si="18">CONCATENATE("description: """,F34,"""", ", ", "note: """,E34,"""",", ","group: """, B34, """",", ","minValue: ", S34,", ","maxValue: ", T34,", ","step: ", U34,", ","units: """, R34, """",", ","defaultValue: ", X34,", ","eventRegistration: ", Y34,)</f>
+        <f t="shared" ref="BG34:BG40" si="17">CONCATENATE("description: """,F34,"""", ", ", "note: """,E34,"""",", ","group: """, B34, """",", ","minValue: ", S34,", ","maxValue: ", T34,", ","step: ", U34,", ","units: """, R34, """",", ","defaultValue: ", X34,", ","eventRegistration: ", Y34,)</f>
         <v>description: "ОТ НН сигн", note: "Контроль оперативного тока НН", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH34" s="37"/>
@@ -22002,11 +22009,11 @@
       </c>
       <c r="H35" s="25"/>
       <c r="I35" s="25">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="J35" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>10</v>
-      </c>
-      <c r="J35" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Внеш. откл</v>
       </c>
       <c r="K35" s="23" t="s">
@@ -22083,14 +22090,14 @@
         <v>0</v>
       </c>
       <c r="AV35" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW35" s="31">
         <v>0</v>
       </c>
       <c r="AX35" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY35" s="31"/>
@@ -22102,7 +22109,7 @@
       <c r="BE35" s="35"/>
       <c r="BF35" s="31"/>
       <c r="BG35" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Внеш. откл", note: "Внешнее отключение", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH35" s="37"/>
@@ -22125,11 +22132,11 @@
       </c>
       <c r="H36" s="25"/>
       <c r="I36" s="25">
+        <f t="shared" si="14"/>
+        <v>18</v>
+      </c>
+      <c r="J36" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>18</v>
-      </c>
-      <c r="J36" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Вых.цепи разобраны</v>
       </c>
       <c r="K36" s="23" t="s">
@@ -22206,14 +22213,14 @@
         <v>0</v>
       </c>
       <c r="AV36" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW36" s="31">
         <v>0</v>
       </c>
       <c r="AX36" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY36" s="31"/>
@@ -22225,7 +22232,7 @@
       <c r="BE36" s="35"/>
       <c r="BF36" s="31"/>
       <c r="BG36" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Вых.цепи разобраны", note: "Выходные цепи разобраны", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH36" s="37"/>
@@ -22248,11 +22255,11 @@
       </c>
       <c r="H37" s="25"/>
       <c r="I37" s="25">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="J37" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>11</v>
-      </c>
-      <c r="J37" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>БИ выведены</v>
       </c>
       <c r="K37" s="23" t="s">
@@ -22329,14 +22336,14 @@
         <v>0</v>
       </c>
       <c r="AV37" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW37" s="31">
         <v>0</v>
       </c>
       <c r="AX37" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY37" s="31"/>
@@ -22348,7 +22355,7 @@
       <c r="BE37" s="35"/>
       <c r="BF37" s="31"/>
       <c r="BG37" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "БИ выведены", note: "БИ выведены", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH37" s="37"/>
@@ -22371,11 +22378,11 @@
       </c>
       <c r="H38" s="25"/>
       <c r="I38" s="25">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="J38" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>17</v>
-      </c>
-      <c r="J38" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Прев. вр. пер. КА</v>
       </c>
       <c r="K38" s="23" t="s">
@@ -22452,14 +22459,14 @@
         <v>0</v>
       </c>
       <c r="AV38" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW38" s="31">
         <v>0</v>
       </c>
       <c r="AX38" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY38" s="31"/>
@@ -22471,7 +22478,7 @@
       <c r="BE38" s="35"/>
       <c r="BF38" s="31"/>
       <c r="BG38" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Прев. вр. пер. КА", note: "Превышение времени переключения КА", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH38" s="37"/>
@@ -22494,11 +22501,11 @@
       </c>
       <c r="H39" s="25"/>
       <c r="I39" s="25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="J39" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>19</v>
-      </c>
-      <c r="J39" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>Общ. внеш. сигн. СС</v>
       </c>
       <c r="K39" s="23" t="s">
@@ -22575,14 +22582,14 @@
         <v>0</v>
       </c>
       <c r="AV39" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW39" s="31">
         <v>0</v>
       </c>
       <c r="AX39" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY39" s="31"/>
@@ -22594,7 +22601,7 @@
       <c r="BE39" s="35"/>
       <c r="BF39" s="31"/>
       <c r="BG39" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "Общ. внеш. сигн. СС", note: "Общий внешний сигнал от СС", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH39" s="37"/>
@@ -22617,11 +22624,11 @@
       </c>
       <c r="H40" s="25"/>
       <c r="I40" s="25">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="J40" s="25" t="str">
         <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="J40" s="25" t="str">
-        <f t="shared" si="16"/>
         <v>IRF</v>
       </c>
       <c r="K40" s="23" t="s">
@@ -22698,14 +22705,14 @@
         <v>0</v>
       </c>
       <c r="AV40" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AW40" s="31">
         <v>0</v>
       </c>
       <c r="AX40" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AY40" s="31"/>
@@ -22717,7 +22724,7 @@
       <c r="BE40" s="35"/>
       <c r="BF40" s="31"/>
       <c r="BG40" s="36" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>description: "IRF", note: "Неисправность терминала", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH40" s="37"/>
@@ -26558,15 +26565,15 @@
       <c r="AW1" s="11"/>
       <c r="AX1" s="11"/>
       <c r="AY1" s="13"/>
-      <c r="AZ1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
+      <c r="AZ1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="61"/>
+      <c r="BB1" s="61"/>
+      <c r="BC1" s="61"/>
+      <c r="BD1" s="61"/>
+      <c r="BE1" s="61"/>
+      <c r="BF1" s="61"/>
     </row>
     <row r="2" spans="1:16379" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -43414,15 +43421,15 @@
       <c r="AX1" s="11"/>
       <c r="AY1" s="11"/>
       <c r="AZ1" s="13"/>
-      <c r="BA1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="60"/>
-      <c r="BF1" s="60"/>
-      <c r="BG1" s="60"/>
+      <c r="BA1" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="61"/>
+      <c r="BC1" s="61"/>
+      <c r="BD1" s="61"/>
+      <c r="BE1" s="61"/>
+      <c r="BF1" s="61"/>
+      <c r="BG1" s="61"/>
     </row>
     <row r="2" spans="1:16380" s="22" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -43446,7 +43453,7 @@
       <c r="G2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="61" t="s">
+      <c r="H2" s="59" t="s">
         <v>254</v>
       </c>
       <c r="I2" s="14" t="s">
